--- a/indata/BCG_latitude.xlsx
+++ b/indata/BCG_latitude.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debebeadewo/Documents/GitHub/Bbuff/indata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C98677F-62B3-014D-AF14-473F9F103888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C433DF-5075-F547-BEB5-D13F86787AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="660" windowWidth="27240" windowHeight="17980" xr2:uid="{3467CD44-BD21-FF44-8808-2553FBEDFEB1}"/>
+    <workbookView xWindow="15100" yWindow="660" windowWidth="15140" windowHeight="17920" activeTab="1" xr2:uid="{3467CD44-BD21-FF44-8808-2553FBEDFEB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="75">
   <si>
     <t>cntry</t>
   </si>
@@ -104,6 +105,9 @@
     <t>Argentina BuenosAires</t>
   </si>
   <si>
+    <t>USAGeorgia</t>
+  </si>
+  <si>
     <t>USAGeorgiaSchool</t>
   </si>
   <si>
@@ -174,6 +178,93 @@
   </si>
   <si>
     <t>Burma</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>BCGPop</t>
+  </si>
+  <si>
+    <t>NoBCGPop</t>
+  </si>
+  <si>
+    <t>TBBCG</t>
+  </si>
+  <si>
+    <t>TBNoBCG</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAIndians </t>
+  </si>
+  <si>
+    <t>UKChildren</t>
+  </si>
+  <si>
+    <t>IndiaMandanpallee</t>
+  </si>
+  <si>
+    <t>PimaArizona</t>
+  </si>
+  <si>
+    <t>SouthAfrica</t>
+  </si>
+  <si>
+    <t>USAChicago</t>
+  </si>
+  <si>
+    <t>USAGeorgeiaAlabama</t>
+  </si>
+  <si>
+    <t>LAT</t>
+  </si>
+  <si>
+    <t>Rosenthal et al,1960</t>
+  </si>
+  <si>
+    <t>Hart and Sutherland,1977</t>
+  </si>
+  <si>
+    <t>Frimodt-Molleretal,1973</t>
+  </si>
+  <si>
+    <t>Stein and Aronson,1953</t>
+  </si>
+  <si>
+    <t>Vandiviere et al, 1973</t>
+  </si>
+  <si>
+    <t>Madras,'1980</t>
+  </si>
+  <si>
+    <t>Coetzee and Berjak, 1968</t>
+  </si>
+  <si>
+    <t>Rosenthal et al,1961</t>
+  </si>
+  <si>
+    <t>Comstock et al, 1974</t>
+  </si>
+  <si>
+    <t>Comstock and Webster,1969</t>
+  </si>
+  <si>
+    <t>Comstock et al,1976</t>
+  </si>
+  <si>
+    <t>IndianUS kids</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>Ferguson and Simes,1949</t>
+  </si>
+  <si>
+    <t>Aronson, 1948</t>
   </si>
 </sst>
 </file>
@@ -216,9 +307,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,26 +645,6 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
-  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
-  <we:alternateReferences>
-    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE73D73-D928-F14F-A36B-0A2E80D6E5CD}">
   <dimension ref="A1:G21"/>
@@ -582,7 +656,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -614,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -637,7 +711,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -660,7 +734,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -674,7 +748,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -683,7 +757,7 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -697,7 +771,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -706,7 +780,7 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -720,7 +794,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -729,7 +803,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -743,7 +817,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -752,7 +826,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -766,13 +840,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -786,13 +860,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -806,16 +880,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -829,16 +903,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
         <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -852,13 +926,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -872,13 +946,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -892,13 +966,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -912,13 +986,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -932,13 +1006,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -952,13 +1026,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
@@ -972,13 +1046,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
         <v>33</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -992,13 +1066,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -1012,13 +1086,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -1028,6 +1102,383 @@
       </c>
       <c r="G21">
         <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302C98BA-2867-B242-9D15-C49C3A8B8278}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2">
+        <v>123</v>
+      </c>
+      <c r="C2">
+        <v>139</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3">
+        <v>306</v>
+      </c>
+      <c r="C3">
+        <v>303</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>29</v>
+      </c>
+      <c r="F3">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4">
+        <v>231</v>
+      </c>
+      <c r="C4">
+        <v>220</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5">
+        <v>13598</v>
+      </c>
+      <c r="C5">
+        <v>12867</v>
+      </c>
+      <c r="D5">
+        <v>62</v>
+      </c>
+      <c r="E5">
+        <v>248</v>
+      </c>
+      <c r="F5">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6">
+        <v>5069</v>
+      </c>
+      <c r="C6">
+        <v>5808</v>
+      </c>
+      <c r="D6">
+        <v>33</v>
+      </c>
+      <c r="E6">
+        <v>47</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <v>1541</v>
+      </c>
+      <c r="C7">
+        <v>1451</v>
+      </c>
+      <c r="D7">
+        <v>180</v>
+      </c>
+      <c r="E7">
+        <v>372</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8">
+        <v>2545</v>
+      </c>
+      <c r="C8">
+        <v>629</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9">
+        <v>88391</v>
+      </c>
+      <c r="C9">
+        <v>88391</v>
+      </c>
+      <c r="D9">
+        <v>505</v>
+      </c>
+      <c r="E9">
+        <v>499</v>
+      </c>
+      <c r="F9">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10">
+        <v>7499</v>
+      </c>
+      <c r="C10">
+        <v>7277</v>
+      </c>
+      <c r="D10">
+        <v>29</v>
+      </c>
+      <c r="E10">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11">
+        <v>1716</v>
+      </c>
+      <c r="C11">
+        <v>1665</v>
+      </c>
+      <c r="D11">
+        <v>17</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+      <c r="F11">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12">
+        <v>50634</v>
+      </c>
+      <c r="C12">
+        <v>27338</v>
+      </c>
+      <c r="D12">
+        <v>186</v>
+      </c>
+      <c r="E12">
+        <v>141</v>
+      </c>
+      <c r="F12">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13">
+        <v>2498</v>
+      </c>
+      <c r="C13">
+        <v>2341</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14">
+        <v>16913</v>
+      </c>
+      <c r="C14">
+        <v>17854</v>
+      </c>
+      <c r="D14">
+        <v>27</v>
+      </c>
+      <c r="E14">
+        <v>29</v>
+      </c>
+      <c r="F14">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
